--- a/13754_Cuenca_Canete/_raw_reportes_xlsx/IDConfig_64975_completo.xlsx
+++ b/13754_Cuenca_Canete/_raw_reportes_xlsx/IDConfig_64975_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re6671a192c8c4b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re68c4f80f22d4246"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4351</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8548</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5039</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3758</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/13754_Cuenca_Canete/_raw_reportes_xlsx/IDConfig_64975_completo.xlsx
+++ b/13754_Cuenca_Canete/_raw_reportes_xlsx/IDConfig_64975_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Re68c4f80f22d4246"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8759ba28caea4fd5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.3919</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6322</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5863</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.7352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.0621</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.9023</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.9238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.5048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3337</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.5976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.8047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9392</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.7696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2662</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2141</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1655</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6799</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.1150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.6844</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7380</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.4399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     15.0370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     16.6190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.8391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.6306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     13.9829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.9577</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.6146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1869</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0602</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.2916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.5571</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.3928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
